--- a/09_ai-transparency-documentation/exercises/starter/model_card.xlsx
+++ b/09_ai-transparency-documentation/exercises/starter/model_card.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Log" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transparency Stack Reference" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Article 11 Reference" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Notes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +48,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="7">
@@ -113,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -169,6 +174,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -607,21 +613,19 @@
       <c r="A11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>CAPSTONE NOTE:</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>REASONING NOTE:</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>In the Security Considerations section, tag attack vectors with ATLAS IDs (e.g., AML.T0015 Evade ML Model, AML.T0051 LLM Prompt Injection). This is the same format as the capstone project's D6 §6 — name the technique with its ATLAS code so it cross-walks cleanly back to the threat model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>For every Model Card cell, Article 11 Crosswalk row, and Gap Log row where you fill in `[Your response here]`, append a short rationale on a new line in the same cell, formatted as: Reasoning: &lt;one sentence on why this content / mapping / gap is the right choice&gt;. Use Alt+Enter (Mac: Option+Enter) for a soft line break inside a cell. This rationale is part of the deliverable — graders look for it on Metrics, Security Considerations, Mitigations, Caveats, all Crosswalk rows you complete, and every Gap Log row you complete.</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
@@ -849,7 +853,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>[Your response here — see pre-filled rows above for tone and depth.]</t>
+          <t>[Your response here — see pre-filled rows above for tone and depth. Append a "Reasoning:" line at the end explaining why these metrics + slices are the right scoping.]</t>
         </is>
       </c>
     </row>
@@ -866,7 +870,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>[Your response here — see pre-filled rows above for tone and depth.]</t>
+          <t>[Your response here — see pre-filled rows above for tone and depth. Append a "Reasoning:" line at the end explaining why these aggregate metrics are the right headline numbers.]</t>
         </is>
       </c>
     </row>
@@ -883,7 +887,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>[Your response here. Tag each attack vector with its ATLAS ID — e.g., [AML.T0015 Evade ML Model] for adversarial perturbations, [AML.T0051 LLM Prompt Injection] for injection payloads in reviews. Same format as the capstone D6 §6 threat model.]</t>
+          <t>[Your response here. Tag each attack vector with its ATLAS ID — e.g., [AML.T0015 Evade ML Model] for adversarial inputs, [AML.T0051 LLM Prompt Injection] for prompt-injection — and include a brief description of how each vector applies to FeedbackIQ-Sentiment-v3.]</t>
         </is>
       </c>
     </row>
@@ -900,7 +904,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>[Your response here — see pre-filled rows above for tone and depth.]</t>
+          <t>[Your response here — see pre-filled rows above for tone and depth. Append a "Reasoning:" line at the end explaining why these mitigations are appropriate and what residual risk remains.]</t>
         </is>
       </c>
     </row>
@@ -917,7 +921,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>[Your response here — see pre-filled rows above for tone and depth.]</t>
+          <t>[Your response here — see pre-filled rows above for tone and depth. Append a "Reasoning:" line at the end explaining the limits + what falls outside this model's competence.]</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1036,17 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — which Article 11 §1 paragraph (a-h) covers Languages + Industry segments?]</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — choose one of: Full / Partial / Out of scope]</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — if Coverage is Partial or Out of scope, name the sister artifact (e.g., Datasheet, Impact Assessment, AUP) picking it up; otherwise enter "—"]</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1058,17 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — which Article 11 §1 paragraph (a-h) covers performance metrics?]</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — choose one of: Full / Partial / Out of scope]</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — if Coverage is Partial or Out of scope, name the sister artifact (e.g., Datasheet, Impact Assessment, AUP) picking it up; otherwise enter "—"]</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1080,17 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — which Article 11 §1 paragraph (a-h) covers cybersecurity / known threats?]</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — choose one of: Full / Partial / Out of scope]</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — if Coverage is Partial or Out of scope, name the sister artifact (e.g., Datasheet, Impact Assessment, AUP) picking it up; otherwise enter "—"]</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1102,17 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — which Article 11 §1 paragraph (a-h) covers foreseeable risks + accuracy limits?]</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — choose one of: Full / Partial / Out of scope]</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — if Coverage is Partial or Out of scope, name the sister artifact (e.g., Datasheet, Impact Assessment, AUP) picking it up; otherwise enter "—"]</t>
         </is>
       </c>
     </row>
@@ -1120,17 +1124,17 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — which Article 11 §1 paragraph (a-h) covers training data / datasets?]</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — choose one of: Full / Partial / Out of scope]</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — if Coverage is Partial or Out of scope, name the sister artifact (e.g., Datasheet, Impact Assessment, AUP) picking it up; otherwise enter "—"]</t>
         </is>
       </c>
     </row>
@@ -1229,22 +1233,22 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — describe what about runtime resources or monitoring is NOT yet covered by this Model Card; see the Article 11 Reference sheet for §1(e) and Row 1 above as a pattern. Append a "Reasoning:" line explaining why this gap belongs in a sister artifact rather than the Model Card.]</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the sister artifact that will carry runtime monitoring + ops content (see the Transparency Stack Reference sheet for artifact options).]</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the functional role/team that owns runtime reliability + monitoring (e.g., Platform / SRE / Ops lead).]</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick a realistic target date in ISO format YYYY-MM-DD; see Row 1 (2026-06-30) for the pattern.]</t>
         </is>
       </c>
     </row>
@@ -1259,22 +1263,22 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — describe what about population-level fundamental-rights risk is NOT yet covered by this Model Card; see the Scenario Brief for the harm scenario and Model Card §Ethical Considerations for the pointer. Append a "Reasoning:" line explaining why population-level analysis belongs in a sister artifact.]</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the sister artifact for population-level rights + harm analysis (see the Transparency Stack Reference sheet).]</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the functional role/team that owns fundamental-rights / impact analysis (e.g., AI Risk / Responsible AI / Compliance lead).]</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick a realistic target date in ISO format YYYY-MM-DD; see Row 1 (2026-06-30) for the pattern.]</t>
         </is>
       </c>
     </row>
@@ -1289,22 +1293,22 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — what is NOT yet covered for Art. 50 deployer transparency? See the Article 11 Reference sheet for the Article 50 row.]</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — which artifact will carry the Article 50 transparency notice (e.g., in-product UI string spec, deployer-facing notice template)?]</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — name the functional role/team that owns deployer-facing transparency UX + notices (e.g., Product / Compliance / Legal lead).]</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here]</t>
+          <t>[Your response here — pick a realistic target date in ISO format YYYY-MM-DD; see Row 1 (2026-06-30) for the pattern.]</t>
         </is>
       </c>
     </row>
@@ -1665,4 +1669,94 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>Specification detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="95" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Article 11 paragraph numbering</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>For brevity, this lesson refers to Article 11 §1(a)–(h). In the published Regulation (EU) 2024/1689, Article 11(1) is a single paragraph that requires technical documentation drawn up before placing on market and "containing, at a minimum, the elements set out in Annex IV." The topical content (general description, training methodologies, monitoring approach, accuracy, cybersecurity, etc.) is structured in Annex IV sections 1–9. The §1(x) labels used here are a pedagogical shorthand for the corresponding Annex IV sections — useful for a Model Card crosswalk that the AI review board can follow row-by-row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="95" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>Annex IV mapping</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>Annex IV §1 = general description (interaction with hardware, software versions, deployment forms). Annex IV §2 = elements of system development including training methodologies (§2(b)), validation (§2(d)), accuracy + cybersecurity (§2(g)). Annex IV §3 = monitoring approach. Annex IV §5 = risk management process. Use the Annex IV section numbers as the canonical statutory anchor when sharing this work outside the lesson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="95" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>AML.T0024 sub-techniques</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>In ATLAS, the parent technique AML.T0024 is "Exfiltration via AI Inference API." The two sub-techniques are: AML.T0024.000 "Infer Training Data Membership" (membership-inference attacks), and AML.T0024.001 "Invert AI Model" (reconstruct training data from model outputs). The Model Card Security Considerations row references AML.T0024.000 for the training-data inference scenario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="95" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>ATLAS naming evolution</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>ATLAS has been renaming the prefix from "ML" to "AI" in some technique names (e.g., AML.T0040 is now "AI Model Inference API Access" in current revisions). Technique IDs are the stable canonical reference; treat the ID as authoritative when the name on the live catalog differs from the workbook label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="95" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Authoritative references</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>Article 11: https://artificialintelligenceact.eu/article/11/  •  Annex IV: https://artificialintelligenceact.eu/annex/4/  •  Article 13: https://artificialintelligenceact.eu/article/13/  •  Article 50: https://artificialintelligenceact.eu/article/50/  •  MITRE ATLAS: https://atlas.mitre.org/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/09_ai-transparency-documentation/exercises/starter/model_card.xlsx
+++ b/09_ai-transparency-documentation/exercises/starter/model_card.xlsx
@@ -588,7 +588,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY CONTEXT: EU AI Act — FeedbackIQ-Sentiment-v3 is classified as Limited Risk in itself (no Annex III hit), but the deployment context with the EU customer triggers Article 13 transparency obligations and the customer's procurement process triggers Article 11 documentation review.</t>
+          <t>REGULATORY CONTEXT: EU AI Act — FeedbackIQ-Sentiment-v3 is classified as Limited Risk in itself (no Annex III hit); Article 13 transparency obligations attach only to high-risk systems, so the binding driver here is the EU customer's procurement process, which contractually requires Article 11-style technical documentation for vendor sign-off.</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Art. 50 — transparency obligation toward end users (deployer)</t>
+          <t>Art. 50 — transparency obligation toward end users (split provider / deployer duties)</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>[Your response here — what is NOT yet covered for Art. 50 deployer transparency? See the Article 11 Reference sheet for the Article 50 row.]</t>
+          <t>[Your response here — what is NOT yet covered for Art. 50 transparency (mind the provider/deployer duty split)? See the Article 11 Reference sheet for the Article 50 row.]</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Disclosure obligations toward end users when they interact with AI systems — chatbot labels, deepfake labels, emotion recognition / biometric categorisation notice. Deployer obligation. Lives outside the Article 11 stack but cross-references it when end-user disclosure is needed.</t>
+          <t>Disclosure obligations toward end users when they interact with AI systems — provider duty for direct-interaction (chatbot) labels and synthetic-content marking (Art. 50(1)–(2)); deployer duty for emotion-recognition / biometric-categorisation notices and deepfake labelling (Art. 50(3)–(4)). Lives outside the Article 11 stack but cross-references it when end-user disclosure is needed.</t>
         </is>
       </c>
     </row>

--- a/09_ai-transparency-documentation/exercises/starter/model_card.xlsx
+++ b/09_ai-transparency-documentation/exercises/starter/model_card.xlsx
@@ -887,7 +887,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>[Your response here. Tag each attack vector with its ATLAS ID — e.g., [AML.T0015 Evade ML Model] for adversarial inputs, [AML.T0051 LLM Prompt Injection] for prompt-injection — and include a brief description of how each vector applies to FeedbackIQ-Sentiment-v3.]</t>
+          <t>[Your response here. Tag each attack vector with its ATLAS ID — e.g., [AML.T0015 Evade AI Model] for adversarial inputs, [AML.T0051 LLM Prompt Injection] for prompt-injection — and include a brief description of how each vector applies to FeedbackIQ-Sentiment-v3.]</t>
         </is>
       </c>
     </row>
